--- a/scenarios/05_tom_optical_designer/5.2_pixel_pitch_optimization/outputs/pixel_pitch_trade_results.xlsx
+++ b/scenarios/05_tom_optical_designer/5.2_pixel_pitch_optimization/outputs/pixel_pitch_trade_results.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -467,8 +467,12 @@
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -516,15 +520,35 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
+          <t>RER [—]</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
           <t>SNR [—]</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>NEDT [K]</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>NIIRS [—]</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Strehl [—]</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>Signal [e⁻]</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>Total Noise [e⁻]</t>
         </is>
@@ -552,14 +576,26 @@
       <c r="G4" s="3" t="n">
         <v>0.7497</v>
       </c>
-      <c r="H4" s="4" t="n">
-        <v>99.09999999999999</v>
-      </c>
-      <c r="I4" s="3" t="n">
+      <c r="H4" s="3" t="n">
+        <v>0.3806</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>113.6</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>0.2498</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" s="3" t="n">
         <v>40000</v>
       </c>
-      <c r="J4" s="3" t="n">
-        <v>403.5</v>
+      <c r="N4" s="3" t="n">
+        <v>352</v>
       </c>
     </row>
     <row r="5">
@@ -584,14 +620,26 @@
       <c r="G5" s="3" t="n">
         <v>0.8387</v>
       </c>
-      <c r="H5" s="5" t="n">
-        <v>188.8</v>
-      </c>
-      <c r="I5" s="3" t="n">
+      <c r="H5" s="3" t="n">
+        <v>0.5374</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>214.1</v>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>0.1326</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" s="3" t="n">
         <v>120000</v>
       </c>
-      <c r="J5" s="3" t="n">
-        <v>635.7</v>
+      <c r="N5" s="3" t="n">
+        <v>560.6</v>
       </c>
     </row>
     <row r="6">
@@ -616,14 +664,26 @@
       <c r="G6" s="3" t="n">
         <v>0.8555</v>
       </c>
-      <c r="H6" s="5" t="n">
-        <v>297.5</v>
-      </c>
-      <c r="I6" s="3" t="n">
+      <c r="H6" s="3" t="n">
+        <v>0.6357</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>333.5</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>0.0851</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" s="3" t="n">
         <v>250000</v>
       </c>
-      <c r="J6" s="3" t="n">
-        <v>840.4</v>
+      <c r="N6" s="3" t="n">
+        <v>749.6</v>
       </c>
     </row>
     <row r="7">
@@ -648,14 +708,26 @@
       <c r="G7" s="6" t="n">
         <v>0.8893</v>
       </c>
-      <c r="H7" s="5" t="n">
-        <v>468.4</v>
-      </c>
-      <c r="I7" s="6" t="n">
+      <c r="H7" s="6" t="n">
+        <v>0.7087</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>516.5</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="K7" s="6" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" s="6" t="n">
         <v>500000</v>
       </c>
-      <c r="J7" s="6" t="n">
-        <v>1067.4</v>
+      <c r="N7" s="6" t="n">
+        <v>968</v>
       </c>
     </row>
     <row r="8">
@@ -680,14 +752,26 @@
       <c r="G8" s="3" t="n">
         <v>0.9157</v>
       </c>
-      <c r="H8" s="5" t="n">
-        <v>725.8</v>
-      </c>
-      <c r="I8" s="3" t="n">
+      <c r="H8" s="3" t="n">
+        <v>0.8118</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>792.3</v>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>0.0358</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" s="3" t="n">
         <v>1070557</v>
       </c>
-      <c r="J8" s="3" t="n">
-        <v>1474.9</v>
+      <c r="N8" s="3" t="n">
+        <v>1351.2</v>
       </c>
     </row>
     <row r="9">
@@ -712,14 +796,26 @@
       <c r="G9" s="3" t="n">
         <v>0.9332</v>
       </c>
-      <c r="H9" s="5" t="n">
-        <v>894.2</v>
-      </c>
-      <c r="I9" s="3" t="n">
+      <c r="H9" s="3" t="n">
+        <v>0.863</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>976.1</v>
+      </c>
+      <c r="J9" s="3" t="n">
+        <v>0.0291</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" s="3" t="n">
         <v>1624952</v>
       </c>
-      <c r="J9" s="3" t="n">
-        <v>1817.1</v>
+      <c r="N9" s="3" t="n">
+        <v>1664.7</v>
       </c>
     </row>
   </sheetData>
@@ -815,7 +911,7 @@
         <v>289.6</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>197.1</v>
+        <v>0</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>0.2</v>
@@ -824,10 +920,10 @@
         <v>8</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>403.5</v>
+        <v>352</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>99.09999999999999</v>
+        <v>113.6</v>
       </c>
     </row>
     <row r="5">
@@ -844,7 +940,7 @@
         <v>440.5</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>299.8</v>
+        <v>0</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>0.2</v>
@@ -853,10 +949,10 @@
         <v>12</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>635.7</v>
+        <v>560.6</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>188.8</v>
+        <v>214.1</v>
       </c>
     </row>
     <row r="6">
@@ -873,7 +969,7 @@
         <v>558.3</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>380</v>
+        <v>0</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>0.3</v>
@@ -882,10 +978,10 @@
         <v>16</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>840.4</v>
+        <v>749.6</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>297.5</v>
+        <v>333.5</v>
       </c>
     </row>
     <row r="7">
@@ -902,7 +998,7 @@
         <v>660.8</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>449.8</v>
+        <v>0</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>0.3</v>
@@ -911,10 +1007,10 @@
         <v>18</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>1067.4</v>
+        <v>968</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>468.4</v>
+        <v>516.5</v>
       </c>
     </row>
     <row r="8">
@@ -931,7 +1027,7 @@
         <v>868.8</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>591.3</v>
+        <v>0</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>0.4</v>
@@ -940,10 +1036,10 @@
         <v>22</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>1474.9</v>
+        <v>1351.2</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>725.8</v>
+        <v>792.3</v>
       </c>
     </row>
     <row r="9">
@@ -960,7 +1056,7 @@
         <v>1070.3</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>728.5</v>
+        <v>0</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>0.5</v>
@@ -969,10 +1065,10 @@
         <v>28</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>1817.1</v>
+        <v>1664.7</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>894.2</v>
+        <v>976.1</v>
       </c>
     </row>
   </sheetData>
@@ -1172,7 +1268,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SNR=99, MTF=0.000 [FAIL]</t>
+          <t>SNR=114, MTF=0.000 [FAIL]</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1280,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SNR=189, MTF=0.181 [ALL PASS]</t>
+          <t>SNR=214, MTF=0.181 [ALL PASS]</t>
         </is>
       </c>
     </row>
@@ -1196,7 +1292,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SNR=297, MTF=0.320 [ALL PASS]</t>
+          <t>SNR=334, MTF=0.320 [ALL PASS]</t>
         </is>
       </c>
     </row>
@@ -1208,7 +1304,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SNR=468, MTF=0.422 [ALL PASS]</t>
+          <t>SNR=517, MTF=0.422 [ALL PASS]</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1316,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SNR=726, MTF=0.559 [FAIL]</t>
+          <t>SNR=792, MTF=0.559 [FAIL]</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1328,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SNR=894, MTF=0.644 [FAIL]</t>
+          <t>SNR=976, MTF=0.644 [FAIL]</t>
         </is>
       </c>
     </row>

--- a/scenarios/05_tom_optical_designer/5.2_pixel_pitch_optimization/outputs/pixel_pitch_trade_results.xlsx
+++ b/scenarios/05_tom_optical_designer/5.2_pixel_pitch_optimization/outputs/pixel_pitch_trade_results.xlsx
@@ -571,13 +571,13 @@
         <v>0</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>0.1786</v>
+        <v>0.1643</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.7497</v>
+        <v>0.7201</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>0.3806</v>
+        <v>0.3643</v>
       </c>
       <c r="I4" s="5" t="n">
         <v>113.6</v>
@@ -586,7 +586,7 @@
         <v>0.2498</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L4" s="3" t="n">
         <v>1</v>
@@ -612,16 +612,16 @@
         <v>41.7</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.181</v>
+        <v>0.1185</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.3652</v>
+        <v>0.3117</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>0.8387</v>
+        <v>0.8314</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>0.5374</v>
+        <v>0.4945</v>
       </c>
       <c r="I5" s="5" t="n">
         <v>214.1</v>
@@ -630,7 +630,7 @@
         <v>0.1326</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L5" s="3" t="n">
         <v>1</v>
@@ -656,16 +656,16 @@
         <v>33.3</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0.3196</v>
+        <v>0.1909</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.4924</v>
+        <v>0.3788</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.8555</v>
+        <v>0.8587</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>0.6357</v>
+        <v>0.5548</v>
       </c>
       <c r="I6" s="5" t="n">
         <v>333.5</v>
@@ -674,7 +674,7 @@
         <v>0.0851</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>1</v>
@@ -700,16 +700,16 @@
         <v>27.8</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>0.4223</v>
+        <v>0.2532</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.6365</v>
+        <v>0.4699</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.8893</v>
+        <v>0.8822</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.7087</v>
+        <v>0.6014</v>
       </c>
       <c r="I7" s="5" t="n">
         <v>516.5</v>
@@ -718,7 +718,7 @@
         <v>0.055</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="L7" s="6" t="n">
         <v>1</v>
@@ -744,16 +744,16 @@
         <v>20.8</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.3661</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>0.7732</v>
+        <v>0.5755</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.9157</v>
+        <v>0.9127</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>0.8118</v>
+        <v>0.6879</v>
       </c>
       <c r="I8" s="5" t="n">
         <v>792.3</v>
@@ -762,7 +762,7 @@
         <v>0.0358</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="L8" s="3" t="n">
         <v>1</v>
@@ -788,16 +788,16 @@
         <v>16.7</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0.6443</v>
+        <v>0.3848</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.8287</v>
+        <v>0.5991</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.9332</v>
+        <v>0.9292</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>0.863</v>
+        <v>0.7131999999999999</v>
       </c>
       <c r="I9" s="5" t="n">
         <v>976.1</v>
@@ -806,7 +806,7 @@
         <v>0.0291</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="L9" s="3" t="n">
         <v>1</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SNR=214, MTF=0.181 [ALL PASS]</t>
+          <t>SNR=214, MTF=0.119 [ALL PASS]</t>
         </is>
       </c>
     </row>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SNR=334, MTF=0.320 [ALL PASS]</t>
+          <t>SNR=334, MTF=0.191 [ALL PASS]</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SNR=517, MTF=0.422 [ALL PASS]</t>
+          <t>SNR=517, MTF=0.253 [ALL PASS]</t>
         </is>
       </c>
     </row>
@@ -1316,7 +1316,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SNR=792, MTF=0.559 [FAIL]</t>
+          <t>SNR=792, MTF=0.366 [FAIL]</t>
         </is>
       </c>
     </row>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SNR=976, MTF=0.644 [FAIL]</t>
+          <t>SNR=976, MTF=0.385 [FAIL]</t>
         </is>
       </c>
     </row>
